--- a/feature engineering.xlsx
+++ b/feature engineering.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repository\thesis\bitcoin-trend-prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E465BB-91CE-44BF-9826-648EACFD1D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D38835B-6D4C-4A6B-B753-2EF4C8661FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feature Engineering" sheetId="1" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
+    <sheet name="featurestore" sheetId="1" r:id="rId1"/>
+    <sheet name="dashboard" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="135">
   <si>
     <t>price</t>
   </si>
@@ -351,28 +351,13 @@
     <t xml:space="preserve">aggregation </t>
   </si>
   <si>
-    <t>5m</t>
-  </si>
-  <si>
-    <t>1m, 5m, 15m, 1h, 4h, 1d</t>
-  </si>
-  <si>
     <t>chart</t>
   </si>
   <si>
-    <t>time frame</t>
-  </si>
-  <si>
-    <t>15m, 1h, 4h, 1d</t>
-  </si>
-  <si>
     <t>trend</t>
   </si>
   <si>
     <t>predict</t>
-  </si>
-  <si>
-    <t>4h, 1d</t>
   </si>
   <si>
     <r>
@@ -439,6 +424,66 @@
   </si>
   <si>
     <t>vwap deviation?</t>
+  </si>
+  <si>
+    <t>tab</t>
+  </si>
+  <si>
+    <t>dual axis line (5m, 15m, 1h, 4h, 1d)</t>
+  </si>
+  <si>
+    <t>line (5m, 15m, 1h, 4h, 1d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">score = (positive − negative) / total </t>
+  </si>
+  <si>
+    <t xml:space="preserve">confidence = (positive + negative) / total </t>
+  </si>
+  <si>
+    <t>3 tables</t>
+  </si>
+  <si>
+    <t>5 tables</t>
+  </si>
+  <si>
+    <t>1 consumer</t>
+  </si>
+  <si>
+    <t>number (1h, 4h, 1d)</t>
+  </si>
+  <si>
+    <t>gauge (1h, 4h, 1d)</t>
+  </si>
+  <si>
+    <t>kline (1m, 5m, 15m, 1h, 4h, 1d)</t>
+  </si>
+  <si>
+    <t>donut distribution (1h, 4h, 1d)</t>
+  </si>
+  <si>
+    <t>1h, 4h, 1d</t>
+  </si>
+  <si>
+    <t>6 tables</t>
+  </si>
+  <si>
+    <t>%negative</t>
+  </si>
+  <si>
+    <t>%positive</t>
+  </si>
+  <si>
+    <t>%neutral</t>
+  </si>
+  <si>
+    <t>word frequency</t>
+  </si>
+  <si>
+    <t>wordcloud (1h, 4h, 1d) thầy Bình đề xuất</t>
+  </si>
+  <si>
+    <t>1 container</t>
   </si>
 </sst>
 </file>
@@ -524,7 +569,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -709,13 +754,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -732,27 +788,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -773,22 +817,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -799,9 +831,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -822,7 +851,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -853,14 +882,100 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1143,94 +1258,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.85546875" style="38" customWidth="1"/>
-    <col min="4" max="4" width="63" style="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.42578125" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="43.42578125" style="38" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="54"/>
-    <col min="13" max="16384" width="9.140625" style="33"/>
+    <col min="1" max="1" width="29.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.85546875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="63" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="43.42578125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="29"/>
+    <col min="13" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="L1" s="31" t="s">
+      <c r="I1" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" s="22" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="35"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" s="9"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="46"/>
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1238,7 +1353,7 @@
         <v>37</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="36"/>
+      <c r="E3" s="27"/>
       <c r="F3" s="2" t="s">
         <v>76</v>
       </c>
@@ -1250,13 +1365,13 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="36"/>
+      <c r="L3" s="27"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="A4" s="46"/>
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1264,7 +1379,7 @@
         <v>40</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="36"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="2" t="s">
         <v>74</v>
       </c>
@@ -1272,13 +1387,13 @@
         <v>92</v>
       </c>
       <c r="H4" s="4"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="36"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="27"/>
     </row>
     <row r="5" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
+      <c r="A5" s="46"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -1286,7 +1401,7 @@
         <v>41</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="36"/>
+      <c r="E5" s="27"/>
       <c r="F5" s="2" t="s">
         <v>73</v>
       </c>
@@ -1294,13 +1409,13 @@
         <v>93</v>
       </c>
       <c r="H5" s="4"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="36"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="27"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+      <c r="A6" s="46"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1308,7 +1423,7 @@
         <v>38</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="28" t="s">
         <v>89</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1318,13 +1433,13 @@
         <v>94</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="36"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="27"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="2" t="s">
         <v>44</v>
       </c>
@@ -1332,70 +1447,70 @@
         <v>39</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="36"/>
-      <c r="G7" s="36"/>
+      <c r="E7" s="27"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="36"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="27"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
+      <c r="A8" s="46"/>
       <c r="B8" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="36"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="36"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="27"/>
     </row>
     <row r="9" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="47"/>
+      <c r="B9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="41"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="32"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="34" t="s">
+      <c r="C10" s="13"/>
+      <c r="D10" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="34" t="s">
+      <c r="E10" s="26"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="35"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="26"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
+      <c r="A11" s="46"/>
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1408,18 +1523,18 @@
       <c r="E11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="36"/>
+      <c r="F11" s="27"/>
       <c r="G11" s="2" t="s">
         <v>96</v>
       </c>
       <c r="H11" s="4"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="36"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="27"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
+      <c r="A12" s="46"/>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1432,18 +1547,18 @@
       <c r="E12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="36"/>
+      <c r="F12" s="27"/>
       <c r="G12" s="2" t="s">
         <v>97</v>
       </c>
       <c r="H12" s="4"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="36"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="27"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
+      <c r="A13" s="46"/>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1456,16 +1571,16 @@
       <c r="E13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="36"/>
+      <c r="F13" s="27"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="36"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="27"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
+      <c r="A14" s="46"/>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1478,159 +1593,159 @@
       <c r="E14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="36"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="2" t="s">
         <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="42" t="s">
+      <c r="L14" s="33" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
+      <c r="A15" s="46"/>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="36"/>
+        <v>108</v>
+      </c>
+      <c r="E15" s="27"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="36"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="27"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="36"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="36"/>
+        <v>109</v>
+      </c>
+      <c r="E16" s="27"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="36"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="27"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
+      <c r="A17" s="46"/>
       <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="36"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="36"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="27"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
+      <c r="A18" s="46"/>
       <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="36"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="27"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="36"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="27"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
+      <c r="A19" s="46"/>
       <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="36"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="27"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="36"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="27"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
+      <c r="A20" s="46"/>
       <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="36"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="27"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="36"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="27"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="47"/>
+      <c r="B21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="41"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="32"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="34" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="34" t="s">
+      <c r="E22" s="26"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="35"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="26"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
+      <c r="A23" s="46"/>
       <c r="B23" s="2" t="s">
         <v>9</v>
       </c>
@@ -1640,7 +1755,7 @@
       <c r="D23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="36"/>
+      <c r="E23" s="27"/>
       <c r="F23" s="2" t="s">
         <v>68</v>
       </c>
@@ -1648,13 +1763,13 @@
         <v>96</v>
       </c>
       <c r="H23" s="4"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="36"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="27"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
+      <c r="A24" s="46"/>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1662,19 +1777,19 @@
         <v>34</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="36"/>
+      <c r="E24" s="27"/>
       <c r="F24" s="2" t="s">
         <v>67</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="36"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="27"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
+      <c r="A25" s="46"/>
       <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
@@ -1682,19 +1797,19 @@
         <v>35</v>
       </c>
       <c r="D25" s="5"/>
-      <c r="E25" s="36"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="36"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="27"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
+      <c r="A26" s="46"/>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
@@ -1702,164 +1817,164 @@
         <v>33</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="36"/>
+      <c r="E26" s="27"/>
       <c r="F26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="36"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="27"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
+      <c r="A27" s="46"/>
       <c r="B27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="43"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="36"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="27"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
+      <c r="A28" s="46"/>
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="36"/>
+      <c r="E28" s="27"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="36"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="27"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
+      <c r="A29" s="46"/>
       <c r="B29" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="36"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="27"/>
       <c r="F29" s="4"/>
       <c r="H29" s="4"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="36"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="27"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="15" t="s">
+      <c r="A30" s="46"/>
+      <c r="B30" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="36"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="27"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
+      <c r="A31" s="46"/>
       <c r="B31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="36"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="27"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="19" t="s">
+      <c r="A32" s="46"/>
+      <c r="B32" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="36"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="27"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="47"/>
+      <c r="B33" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="41"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="32"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="35"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="26"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
+      <c r="A35" s="46"/>
       <c r="B35" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="36"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="27"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="36"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="27"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
+      <c r="A36" s="46"/>
       <c r="B36" s="2" t="s">
         <v>23</v>
       </c>
@@ -1882,10 +1997,10 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="36"/>
+      <c r="L36" s="27"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="2" t="s">
         <v>24</v>
       </c>
@@ -1903,15 +2018,15 @@
         <v>98</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="36"/>
+      <c r="L37" s="27"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
+      <c r="A38" s="46"/>
       <c r="B38" s="2" t="s">
         <v>25</v>
       </c>
@@ -1919,7 +2034,7 @@
         <v>30</v>
       </c>
       <c r="D38" s="5"/>
-      <c r="E38" s="36"/>
+      <c r="E38" s="27"/>
       <c r="F38" s="2" t="s">
         <v>71</v>
       </c>
@@ -1927,13 +2042,13 @@
         <v>100</v>
       </c>
       <c r="H38" s="4"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="36"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="27"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
+      <c r="A39" s="46"/>
       <c r="B39" s="2" t="s">
         <v>26</v>
       </c>
@@ -1948,21 +2063,21 @@
         <v>100</v>
       </c>
       <c r="H39" s="4"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="36"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="27"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
+      <c r="A40" s="46"/>
       <c r="B40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
       <c r="F40" s="2" t="s">
         <v>71</v>
       </c>
@@ -1970,245 +2085,213 @@
         <v>100</v>
       </c>
       <c r="H40" s="4"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="36"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="27"/>
     </row>
     <row r="41" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10" t="s">
+      <c r="A41" s="47"/>
+      <c r="B41" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="10" t="s">
+      <c r="D41" s="14"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="41"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="32"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="35"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="26"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
+      <c r="A43" s="46"/>
       <c r="B43" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="36"/>
+      <c r="E43" s="27"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="36"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="27"/>
     </row>
     <row r="44" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10" t="s">
+      <c r="A44" s="47"/>
+      <c r="B44" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="10" t="s">
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="41"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="32"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="49" t="s">
+      <c r="B45" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C45" s="49"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="36" t="s">
+      <c r="A46" s="46"/>
+      <c r="B46" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="36"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="36"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="27"/>
+      <c r="L46" s="27"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="36" t="s">
+      <c r="A47" s="46"/>
+      <c r="B47" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="36"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="36"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
+      <c r="K47" s="27"/>
+      <c r="L47" s="27"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="36" t="s">
+      <c r="A48" s="46"/>
+      <c r="B48" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="36"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="36"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
     </row>
     <row r="49" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="41" t="s">
+      <c r="A49" s="47"/>
+      <c r="B49" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="41"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="R52" s="55"/>
+      <c r="R52" s="44"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="R53" s="55"/>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D56" s="56"/>
+      <c r="R53" s="44"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="B57" s="53"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="56"/>
+      <c r="A57" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="53"/>
-      <c r="B58" s="53"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="56"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="53"/>
-      <c r="B59" s="53"/>
-      <c r="C59" s="53"/>
-      <c r="D59" s="56"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="49"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="53"/>
-      <c r="B60" s="53"/>
-      <c r="C60" s="53"/>
-      <c r="D60" s="56"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="53"/>
-      <c r="B61" s="53"/>
-      <c r="C61" s="53"/>
-      <c r="D61" s="56"/>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D62" s="56"/>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D63" s="56"/>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D64" s="56"/>
-    </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D65" s="56"/>
-    </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D66" s="56"/>
-    </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D67" s="56"/>
-    </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D68" s="56"/>
-    </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D69" s="56"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A21"/>
     <mergeCell ref="A45:A49"/>
     <mergeCell ref="A34:A41"/>
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="A22:A33"/>
     <mergeCell ref="A57:C61"/>
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A10:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2216,327 +2299,461 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2470E19-6902-46D4-AC65-7A0C7AD1873B}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50" style="74" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:8" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="59">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="60"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="60"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="68"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="60"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="68"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="60"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="68"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="60"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="60"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="60"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="60"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="60"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="60"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="61"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="59">
+        <v>2</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="52"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="60"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="60"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="60"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="68"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="60"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="60"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="71"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="60"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="61"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="71"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="59">
+        <v>3</v>
+      </c>
+      <c r="B22" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="64"/>
+      <c r="E22" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="52"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="60"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="64"/>
+      <c r="E23" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="60"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="64"/>
+      <c r="E24" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="60"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="64"/>
+      <c r="E25" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="60"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="60"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="16"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="61"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="53"/>
+      <c r="B29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="20">
-        <v>1</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="20">
-        <v>2</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="20">
-        <v>3</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="20">
-        <v>4</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
-      <c r="B24" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="21">
-        <v>5</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>110</v>
-      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="E16:E17"/>
+  <mergeCells count="18">
+    <mergeCell ref="H2:H28"/>
+    <mergeCell ref="A22:A28"/>
+    <mergeCell ref="F14:F21"/>
+    <mergeCell ref="F2:F13"/>
+    <mergeCell ref="G14:G21"/>
+    <mergeCell ref="G2:G13"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="F22:F28"/>
+    <mergeCell ref="G22:G28"/>
+    <mergeCell ref="B2:B13"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E3:E8"/>
+    <mergeCell ref="E18:E19"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="A14:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="E16:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/feature engineering.xlsx
+++ b/feature engineering.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repository\thesis\bitcoin-trend-prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D38835B-6D4C-4A6B-B753-2EF4C8661FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608C35EE-3866-4512-9158-34FE13B21CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,21 +885,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -913,68 +898,83 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1313,7 +1313,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="71" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="13" t="s">
@@ -1345,7 +1345,7 @@
       <c r="L2" s="26"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1371,7 +1371,7 @@
       <c r="L3" s="27"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
+      <c r="A4" s="72"/>
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1393,7 +1393,7 @@
       <c r="L4" s="27"/>
     </row>
     <row r="5" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
+      <c r="A5" s="72"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -1415,7 +1415,7 @@
       <c r="L5" s="27"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
+      <c r="A6" s="72"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1439,7 +1439,7 @@
       <c r="L6" s="27"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
+      <c r="A7" s="72"/>
       <c r="B7" s="2" t="s">
         <v>44</v>
       </c>
@@ -1456,7 +1456,7 @@
       <c r="L7" s="27"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
+      <c r="A8" s="72"/>
       <c r="B8" s="2" t="s">
         <v>45</v>
       </c>
@@ -1472,7 +1472,7 @@
       <c r="L8" s="27"/>
     </row>
     <row r="9" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47"/>
+      <c r="A9" s="73"/>
       <c r="B9" s="14" t="s">
         <v>29</v>
       </c>
@@ -1488,7 +1488,7 @@
       <c r="L9" s="32"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="71" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -1510,7 +1510,7 @@
       <c r="L10" s="26"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
+      <c r="A11" s="72"/>
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1534,7 +1534,7 @@
       <c r="L11" s="27"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
+      <c r="A12" s="72"/>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1558,7 +1558,7 @@
       <c r="L12" s="27"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="46"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="L13" s="27"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
+      <c r="A14" s="72"/>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
+      <c r="A15" s="72"/>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
@@ -1626,7 +1626,7 @@
       <c r="L15" s="27"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="46"/>
+      <c r="A16" s="72"/>
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1644,7 +1644,7 @@
       <c r="L16" s="27"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="46"/>
+      <c r="A17" s="72"/>
       <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
@@ -1660,7 +1660,7 @@
       <c r="L17" s="27"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
+      <c r="A18" s="72"/>
       <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
@@ -1675,7 +1675,7 @@
       <c r="L18" s="27"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
+      <c r="A19" s="72"/>
       <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
@@ -1691,7 +1691,7 @@
       <c r="L19" s="27"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
+      <c r="A20" s="72"/>
       <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
@@ -1707,7 +1707,7 @@
       <c r="L20" s="27"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="47"/>
+      <c r="A21" s="73"/>
       <c r="B21" s="10" t="s">
         <v>19</v>
       </c>
@@ -1723,7 +1723,7 @@
       <c r="L21" s="32"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="71" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="9" t="s">
@@ -1745,7 +1745,7 @@
       <c r="L22" s="26"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="46"/>
+      <c r="A23" s="72"/>
       <c r="B23" s="2" t="s">
         <v>9</v>
       </c>
@@ -1769,7 +1769,7 @@
       <c r="L23" s="27"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="46"/>
+      <c r="A24" s="72"/>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1789,7 +1789,7 @@
       <c r="L24" s="27"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="46"/>
+      <c r="A25" s="72"/>
       <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="L25" s="27"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
+      <c r="A26" s="72"/>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
@@ -1829,7 +1829,7 @@
       <c r="L26" s="27"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="46"/>
+      <c r="A27" s="72"/>
       <c r="B27" s="5" t="s">
         <v>13</v>
       </c>
@@ -1845,7 +1845,7 @@
       <c r="L27" s="27"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="46"/>
+      <c r="A28" s="72"/>
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
@@ -1861,7 +1861,7 @@
       <c r="L28" s="27"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="46"/>
+      <c r="A29" s="72"/>
       <c r="B29" s="5" t="s">
         <v>15</v>
       </c>
@@ -1876,7 +1876,7 @@
       <c r="L29" s="27"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="46"/>
+      <c r="A30" s="72"/>
       <c r="B30" s="11" t="s">
         <v>16</v>
       </c>
@@ -1892,7 +1892,7 @@
       <c r="L30" s="27"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="46"/>
+      <c r="A31" s="72"/>
       <c r="B31" s="5" t="s">
         <v>17</v>
       </c>
@@ -1908,7 +1908,7 @@
       <c r="L31" s="27"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="46"/>
+      <c r="A32" s="72"/>
       <c r="B32" s="15" t="s">
         <v>18</v>
       </c>
@@ -1924,7 +1924,7 @@
       <c r="L32" s="27"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="47"/>
+      <c r="A33" s="73"/>
       <c r="B33" s="10" t="s">
         <v>19</v>
       </c>
@@ -1940,7 +1940,7 @@
       <c r="L33" s="32"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="74" t="s">
         <v>20</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -1958,7 +1958,7 @@
       <c r="L34" s="26"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="46"/>
+      <c r="A35" s="72"/>
       <c r="B35" s="4" t="s">
         <v>22</v>
       </c>
@@ -1974,7 +1974,7 @@
       <c r="L35" s="27"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="46"/>
+      <c r="A36" s="72"/>
       <c r="B36" s="2" t="s">
         <v>23</v>
       </c>
@@ -2000,7 +2000,7 @@
       <c r="L36" s="27"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="46"/>
+      <c r="A37" s="72"/>
       <c r="B37" s="2" t="s">
         <v>24</v>
       </c>
@@ -2026,7 +2026,7 @@
       <c r="L37" s="27"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="46"/>
+      <c r="A38" s="72"/>
       <c r="B38" s="2" t="s">
         <v>25</v>
       </c>
@@ -2048,7 +2048,7 @@
       <c r="L38" s="27"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="46"/>
+      <c r="A39" s="72"/>
       <c r="B39" s="2" t="s">
         <v>26</v>
       </c>
@@ -2069,7 +2069,7 @@
       <c r="L39" s="27"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="46"/>
+      <c r="A40" s="72"/>
       <c r="B40" s="2" t="s">
         <v>28</v>
       </c>
@@ -2091,7 +2091,7 @@
       <c r="L40" s="27"/>
     </row>
     <row r="41" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="47"/>
+      <c r="A41" s="73"/>
       <c r="B41" s="7" t="s">
         <v>27</v>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="L41" s="32"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="45" t="s">
+      <c r="A42" s="74" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -2131,7 +2131,7 @@
       <c r="L42" s="26"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="46"/>
+      <c r="A43" s="72"/>
       <c r="B43" s="4" t="s">
         <v>6</v>
       </c>
@@ -2147,7 +2147,7 @@
       <c r="L43" s="27"/>
     </row>
     <row r="44" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="47"/>
+      <c r="A44" s="73"/>
       <c r="B44" s="7" t="s">
         <v>7</v>
       </c>
@@ -2169,7 +2169,7 @@
       <c r="L44" s="32"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="74" t="s">
         <v>56</v>
       </c>
       <c r="B45" s="40" t="s">
@@ -2187,7 +2187,7 @@
       <c r="L45" s="26"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="46"/>
+      <c r="A46" s="72"/>
       <c r="B46" s="27" t="s">
         <v>58</v>
       </c>
@@ -2203,7 +2203,7 @@
       <c r="L46" s="27"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="46"/>
+      <c r="A47" s="72"/>
       <c r="B47" s="27" t="s">
         <v>59</v>
       </c>
@@ -2219,7 +2219,7 @@
       <c r="L47" s="27"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="46"/>
+      <c r="A48" s="72"/>
       <c r="B48" s="27" t="s">
         <v>60</v>
       </c>
@@ -2235,7 +2235,7 @@
       <c r="L48" s="27"/>
     </row>
     <row r="49" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="47"/>
+      <c r="A49" s="73"/>
       <c r="B49" s="32" t="s">
         <v>61</v>
       </c>
@@ -2257,41 +2257,41 @@
       <c r="R53" s="44"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="49" t="s">
+      <c r="A57" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="B57" s="49"/>
-      <c r="C57" s="49"/>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="49"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
+      <c r="A58" s="75"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="75"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="49"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
+      <c r="A59" s="75"/>
+      <c r="B59" s="75"/>
+      <c r="C59" s="75"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="49"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
+      <c r="A60" s="75"/>
+      <c r="B60" s="75"/>
+      <c r="C60" s="75"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="49"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
+      <c r="A61" s="75"/>
+      <c r="B61" s="75"/>
+      <c r="C61" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A57:C61"/>
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="A10:A21"/>
     <mergeCell ref="A45:A49"/>
     <mergeCell ref="A34:A41"/>
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="A22:A33"/>
-    <mergeCell ref="A57:C61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2305,316 +2305,316 @@
     <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50" style="74" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50" style="56" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="57" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:8" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="49" t="s">
         <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="67" t="s">
         <v>49</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="16"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="52" t="s">
+      <c r="E2" s="53"/>
+      <c r="F2" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="58" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="60"/>
-      <c r="B3" s="56"/>
+      <c r="B3" s="68"/>
       <c r="C3" s="19" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="60"/>
-      <c r="B4" s="56"/>
+      <c r="B4" s="68"/>
       <c r="C4" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="68"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="60"/>
-      <c r="B5" s="56"/>
+      <c r="B5" s="68"/>
       <c r="C5" s="19" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="68"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="60"/>
-      <c r="B6" s="56"/>
+      <c r="B6" s="68"/>
       <c r="C6" s="19" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="60"/>
-      <c r="B7" s="56"/>
+      <c r="B7" s="68"/>
       <c r="C7" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="16"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="60"/>
-      <c r="B8" s="56"/>
+      <c r="B8" s="68"/>
       <c r="C8" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="16"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="60"/>
-      <c r="B9" s="56"/>
+      <c r="B9" s="68"/>
       <c r="C9" s="17" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="16"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="60"/>
-      <c r="B10" s="56"/>
+      <c r="B10" s="68"/>
       <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="16"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="60"/>
-      <c r="B11" s="56"/>
+      <c r="B11" s="68"/>
       <c r="C11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="16"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="60"/>
-      <c r="B12" s="56"/>
+      <c r="B12" s="68"/>
       <c r="C12" s="17" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="16"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
-      <c r="B13" s="56"/>
+      <c r="B13" s="68"/>
       <c r="C13" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="59">
         <v>2</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="68" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="16"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="52" t="s">
+      <c r="E14" s="52"/>
+      <c r="F14" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="G14" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="52"/>
+      <c r="H14" s="58"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="60"/>
-      <c r="B15" s="56"/>
+      <c r="B15" s="68"/>
       <c r="C15" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="16"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="60"/>
-      <c r="B16" s="56"/>
+      <c r="B16" s="68"/>
       <c r="C16" s="19" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="60"/>
-      <c r="B17" s="56"/>
+      <c r="B17" s="68"/>
       <c r="C17" s="19" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="68"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="60"/>
-      <c r="B18" s="56"/>
+      <c r="B18" s="68"/>
       <c r="C18" s="19" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="70" t="s">
+      <c r="E18" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="60"/>
-      <c r="B19" s="56"/>
+      <c r="B19" s="68"/>
       <c r="C19" s="19" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="71"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="60"/>
-      <c r="B20" s="56"/>
+      <c r="B20" s="68"/>
       <c r="C20" s="19" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="70" t="s">
+      <c r="E20" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
-      <c r="B21" s="56"/>
+      <c r="B21" s="68"/>
       <c r="C21" s="19" t="s">
         <v>27</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="71"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="59">
@@ -2626,17 +2626,17 @@
       <c r="C22" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="72" t="s">
+      <c r="D22" s="51"/>
+      <c r="E22" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="52" t="s">
+      <c r="F22" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="52" t="s">
+      <c r="G22" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="52"/>
+      <c r="H22" s="58"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="60"/>
@@ -2644,13 +2644,13 @@
       <c r="C23" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="72" t="s">
+      <c r="D23" s="51"/>
+      <c r="E23" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="60"/>
@@ -2658,13 +2658,13 @@
       <c r="C24" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="72" t="s">
+      <c r="D24" s="51"/>
+      <c r="E24" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="60"/>
@@ -2672,13 +2672,13 @@
       <c r="C25" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="72" t="s">
+      <c r="D25" s="51"/>
+      <c r="E25" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60"/>
@@ -2687,12 +2687,12 @@
         <v>129</v>
       </c>
       <c r="D26" s="16"/>
-      <c r="E26" s="70" t="s">
+      <c r="E26" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60"/>
@@ -2701,25 +2701,25 @@
         <v>130</v>
       </c>
       <c r="D27" s="16"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="61"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="63"/>
       <c r="C28" s="20" t="s">
         <v>131</v>
       </c>
       <c r="D28" s="16"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="53"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
@@ -2730,14 +2730,16 @@
       <c r="E29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="53"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A22:A29"/>
     <mergeCell ref="H2:H28"/>
-    <mergeCell ref="A22:A28"/>
     <mergeCell ref="F14:F21"/>
     <mergeCell ref="F2:F13"/>
     <mergeCell ref="G14:G21"/>
@@ -2752,8 +2754,6 @@
     <mergeCell ref="E3:E8"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="A2:A13"/>
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="E16:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/feature engineering.xlsx
+++ b/feature engineering.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repository\thesis\bitcoin-trend-prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961E254B-6DE0-4808-BD89-0FFB6EBE2BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE7A0C8-58E2-44E7-890B-CBF5607EFC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1598,15 +1598,6 @@
     <t>(1) aggregation (1d)</t>
   </si>
   <si>
-    <t>(6) momentum (3d, 7d, 14d, 30d)</t>
-  </si>
-  <si>
-    <t>(4) rolling(3d, 7d, 14d, 30d)</t>
-  </si>
-  <si>
-    <t>(7) lag (1d, 2d, 3d, 5d, 7d, 14d, 30d)</t>
-  </si>
-  <si>
     <t>(2) relative range</t>
   </si>
   <si>
@@ -1790,6 +1781,15 @@
   </si>
   <si>
     <t xml:space="preserve">(2) imbalance: [buy, tick up] count </t>
+  </si>
+  <si>
+    <t>(4) rolling(4, 8, 16, 32)</t>
+  </si>
+  <si>
+    <t>(6) momentum(4, 8, 16, 32)</t>
+  </si>
+  <si>
+    <t>(7) lag (1, 2, 4, 8, 16, 32)</t>
   </si>
 </sst>
 </file>
@@ -2361,6 +2361,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2452,7 +2453,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -2749,10 +2749,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="71"/>
+      <c r="B1" s="72"/>
       <c r="C1" s="11" t="s">
         <v>72</v>
       </c>
@@ -2770,10 +2770,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="72" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="22" t="s">
@@ -2793,8 +2793,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
       <c r="C3" s="22" t="s">
         <v>56</v>
       </c>
@@ -2812,8 +2812,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="71"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="72"/>
       <c r="C4" s="22" t="s">
         <v>62</v>
       </c>
@@ -2831,8 +2831,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="71"/>
+      <c r="A5" s="72"/>
+      <c r="B5" s="72"/>
       <c r="C5" s="22" t="s">
         <v>63</v>
       </c>
@@ -2850,8 +2850,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="71"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="72"/>
       <c r="C6" s="21" t="s">
         <v>65</v>
       </c>
@@ -2869,8 +2869,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="71"/>
-      <c r="B7" s="71"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="72"/>
       <c r="C7" s="21" t="s">
         <v>61</v>
       </c>
@@ -2888,8 +2888,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="71"/>
+      <c r="A8" s="72"/>
+      <c r="B8" s="72"/>
       <c r="C8" s="21" t="s">
         <v>57</v>
       </c>
@@ -2907,8 +2907,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="71"/>
-      <c r="B9" s="71"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="72"/>
       <c r="C9" s="20" t="s">
         <v>64</v>
       </c>
@@ -2924,8 +2924,8 @@
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="71"/>
-      <c r="B10" s="71"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="72"/>
       <c r="C10" s="20" t="s">
         <v>59</v>
       </c>
@@ -2941,8 +2941,8 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="71"/>
-      <c r="B11" s="71"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="72"/>
       <c r="C11" s="20" t="s">
         <v>58</v>
       </c>
@@ -2958,8 +2958,8 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="71" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="72" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="21" t="s">
@@ -2979,8 +2979,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
-      <c r="B13" s="71"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="72"/>
       <c r="C13" s="22" t="s">
         <v>56</v>
       </c>
@@ -2998,8 +2998,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="71"/>
-      <c r="B14" s="71"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
       <c r="C14" s="20" t="s">
         <v>64</v>
       </c>
@@ -3015,10 +3015,10 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="71"/>
+      <c r="B15" s="72"/>
       <c r="C15" s="11" t="s">
         <v>76</v>
       </c>
@@ -3036,8 +3036,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="71"/>
-      <c r="B16" s="71"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="72"/>
       <c r="C16" s="11" t="s">
         <v>77</v>
       </c>
@@ -3055,22 +3055,22 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="70" t="s">
+      <c r="A18" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="70"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
       <c r="G19" s="23"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3129,10 +3129,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="40" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="57"/>
+      <c r="B1" s="58"/>
       <c r="C1" s="41" t="s">
         <v>72</v>
       </c>
@@ -3149,53 +3149,53 @@
         <v>157</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="K1" s="41" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="59" t="s">
         <v>60</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>91</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="33" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I2" s="43" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="59"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="60"/>
       <c r="D3" s="27" t="s">
         <v>0</v>
       </c>
@@ -3212,9 +3212,9 @@
       <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="59"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="60"/>
       <c r="D4" s="27" t="s">
         <v>1</v>
       </c>
@@ -3237,14 +3237,14 @@
       <c r="K4" s="29"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="59"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="60"/>
       <c r="D5" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" s="29" t="s">
@@ -3262,9 +3262,9 @@
       <c r="K5" s="29"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="59"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="60"/>
       <c r="D6" s="30" t="s">
         <v>3</v>
       </c>
@@ -3279,9 +3279,9 @@
       <c r="K6" s="29"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="59"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="60"/>
       <c r="D7" s="27" t="s">
         <v>92</v>
       </c>
@@ -3289,49 +3289,49 @@
         <v>115</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G7" s="29"/>
       <c r="H7" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="I7" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="I7" s="29" t="s">
-        <v>252</v>
-      </c>
       <c r="J7" s="29" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K7" s="29"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="67"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="60"/>
+      <c r="A8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="31" t="s">
         <v>93</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I8" s="45" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J8" s="37" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="K8" s="37"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="67"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="58" t="s">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="59" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="25" t="s">
@@ -3349,14 +3349,14 @@
         <v>151</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K9" s="33"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="67"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="59"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="60"/>
       <c r="D10" s="27" t="s">
         <v>5</v>
       </c>
@@ -3375,9 +3375,9 @@
       <c r="K10" s="29"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="67"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="59"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="60"/>
       <c r="D11" s="27" t="s">
         <v>6</v>
       </c>
@@ -3396,9 +3396,9 @@
       <c r="K11" s="29"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="67"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="59"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="60"/>
       <c r="D12" s="27" t="s">
         <v>7</v>
       </c>
@@ -3417,9 +3417,9 @@
       <c r="K12" s="29"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="67"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="59"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="60"/>
       <c r="D13" s="27" t="s">
         <v>8</v>
       </c>
@@ -3439,16 +3439,16 @@
         <v>141</v>
       </c>
       <c r="J13" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K13" s="44" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="59"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="60"/>
       <c r="D14" s="27" t="s">
         <v>10</v>
       </c>
@@ -3463,9 +3463,9 @@
       <c r="K14" s="29"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="67"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="59"/>
+      <c r="A15" s="68"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="60"/>
       <c r="D15" s="27" t="s">
         <v>9</v>
       </c>
@@ -3488,9 +3488,9 @@
       <c r="K15" s="29"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="59"/>
+      <c r="A16" s="68"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="60"/>
       <c r="D16" s="27" t="s">
         <v>11</v>
       </c>
@@ -3513,9 +3513,9 @@
       <c r="K16" s="29"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="59"/>
+      <c r="A17" s="68"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="60"/>
       <c r="D17" s="27" t="s">
         <v>12</v>
       </c>
@@ -3538,9 +3538,9 @@
       <c r="K17" s="29"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="59"/>
+      <c r="A18" s="68"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="60"/>
       <c r="D18" s="27" t="s">
         <v>13</v>
       </c>
@@ -3563,9 +3563,9 @@
       <c r="K18" s="29"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="59"/>
+      <c r="A19" s="68"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="60"/>
       <c r="D19" s="27" t="s">
         <v>14</v>
       </c>
@@ -3588,32 +3588,32 @@
       <c r="K19" s="29"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="67"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="60"/>
+      <c r="A20" s="68"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="36" t="s">
         <v>15</v>
       </c>
       <c r="E20" s="37"/>
-      <c r="F20" s="86" t="s">
-        <v>247</v>
+      <c r="F20" s="55" t="s">
+        <v>244</v>
       </c>
       <c r="G20" s="37"/>
       <c r="H20" s="29" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K20" s="37"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="58" t="s">
+      <c r="A21" s="68"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="59" t="s">
         <v>63</v>
       </c>
       <c r="D21" s="25" t="s">
@@ -3630,9 +3630,9 @@
       <c r="K21" s="33"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="67"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="59"/>
+      <c r="A22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="27" t="s">
         <v>5</v>
       </c>
@@ -3650,9 +3650,9 @@
       <c r="S22" s="40"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="67"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="68"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="60"/>
       <c r="D23" s="27" t="s">
         <v>6</v>
       </c>
@@ -3667,9 +3667,9 @@
       <c r="K23" s="29"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="67"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="59"/>
+      <c r="A24" s="68"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="60"/>
       <c r="D24" s="27" t="s">
         <v>7</v>
       </c>
@@ -3684,9 +3684,9 @@
       <c r="K24" s="29"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="67"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="59"/>
+      <c r="A25" s="68"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="60"/>
       <c r="D25" s="27" t="s">
         <v>8</v>
       </c>
@@ -3707,9 +3707,9 @@
       <c r="K25" s="29"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="67"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="59"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="60"/>
       <c r="D26" s="27" t="s">
         <v>10</v>
       </c>
@@ -3722,9 +3722,9 @@
       <c r="K26" s="29"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="67"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="59"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="30" t="s">
         <v>9</v>
       </c>
@@ -3737,9 +3737,9 @@
       <c r="K27" s="29"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="67"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="59"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="60"/>
       <c r="D28" s="30" t="s">
         <v>11</v>
       </c>
@@ -3752,9 +3752,9 @@
       <c r="K28" s="29"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="67"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="59"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="60"/>
       <c r="D29" s="30" t="s">
         <v>12</v>
       </c>
@@ -3767,9 +3767,9 @@
       <c r="K29" s="29"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="67"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="59"/>
+      <c r="A30" s="68"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="60"/>
       <c r="D30" s="30" t="s">
         <v>13</v>
       </c>
@@ -3782,9 +3782,9 @@
       <c r="K30" s="29"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="67"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="59"/>
+      <c r="A31" s="68"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="60"/>
       <c r="D31" s="30" t="s">
         <v>14</v>
       </c>
@@ -3797,9 +3797,9 @@
       <c r="K31" s="29"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="67"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="60"/>
+      <c r="A32" s="68"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="61"/>
       <c r="D32" s="36" t="s">
         <v>15</v>
       </c>
@@ -3812,9 +3812,9 @@
       <c r="K32" s="37"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="67"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="58" t="s">
+      <c r="A33" s="68"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="59" t="s">
         <v>62</v>
       </c>
       <c r="D33" s="25" t="s">
@@ -3829,9 +3829,9 @@
       <c r="K33" s="33"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="67"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="59"/>
+      <c r="A34" s="68"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="60"/>
       <c r="D34" s="30" t="s">
         <v>18</v>
       </c>
@@ -3844,9 +3844,9 @@
       <c r="K34" s="29"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="67"/>
-      <c r="B35" s="67"/>
-      <c r="C35" s="59"/>
+      <c r="A35" s="68"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="60"/>
       <c r="D35" s="27" t="s">
         <v>19</v>
       </c>
@@ -3869,9 +3869,9 @@
       <c r="K35" s="29"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="67"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="59"/>
+      <c r="A36" s="68"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="60"/>
       <c r="D36" s="27" t="s">
         <v>20</v>
       </c>
@@ -3894,9 +3894,9 @@
       <c r="K36" s="29"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="67"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="59"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="60"/>
       <c r="D37" s="27" t="s">
         <v>21</v>
       </c>
@@ -3917,9 +3917,9 @@
       <c r="K37" s="29"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="67"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="59"/>
+      <c r="A38" s="68"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="60"/>
       <c r="D38" s="27" t="s">
         <v>22</v>
       </c>
@@ -3940,9 +3940,9 @@
       <c r="K38" s="29"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="67"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="59"/>
+      <c r="A39" s="68"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="60"/>
       <c r="D39" s="27" t="s">
         <v>24</v>
       </c>
@@ -3963,9 +3963,9 @@
       <c r="K39" s="29"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="67"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="60"/>
+      <c r="A40" s="68"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="61"/>
       <c r="D40" s="31" t="s">
         <v>23</v>
       </c>
@@ -3986,11 +3986,11 @@
       <c r="K40" s="37"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="67"/>
-      <c r="B41" s="68" t="s">
+      <c r="A41" s="68"/>
+      <c r="B41" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="59" t="s">
         <v>56</v>
       </c>
       <c r="D41" s="25" t="s">
@@ -4005,9 +4005,9 @@
       <c r="K41" s="33"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="67"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="59"/>
+      <c r="A42" s="68"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="60"/>
       <c r="D42" s="30" t="s">
         <v>5</v>
       </c>
@@ -4020,9 +4020,9 @@
       <c r="K42" s="29"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="67"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="59"/>
+      <c r="A43" s="68"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="60"/>
       <c r="D43" s="30" t="s">
         <v>6</v>
       </c>
@@ -4035,9 +4035,9 @@
       <c r="K43" s="29"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="67"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="59"/>
+      <c r="A44" s="68"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="60"/>
       <c r="D44" s="30" t="s">
         <v>7</v>
       </c>
@@ -4050,9 +4050,9 @@
       <c r="K44" s="29"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="67"/>
-      <c r="B45" s="67"/>
-      <c r="C45" s="59"/>
+      <c r="A45" s="68"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="60"/>
       <c r="D45" s="30" t="s">
         <v>8</v>
       </c>
@@ -4065,9 +4065,9 @@
       <c r="K45" s="29"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="67"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="59"/>
+      <c r="A46" s="68"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="60"/>
       <c r="D46" s="27" t="s">
         <v>10</v>
       </c>
@@ -4080,9 +4080,9 @@
       <c r="K46" s="29"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="67"/>
-      <c r="B47" s="67"/>
-      <c r="C47" s="59"/>
+      <c r="A47" s="68"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="60"/>
       <c r="D47" s="27" t="s">
         <v>9</v>
       </c>
@@ -4105,9 +4105,9 @@
       <c r="K47" s="29"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="67"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="59"/>
+      <c r="A48" s="68"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="60"/>
       <c r="D48" s="27" t="s">
         <v>11</v>
       </c>
@@ -4130,9 +4130,9 @@
       <c r="K48" s="29"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="67"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="59"/>
+      <c r="A49" s="68"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="60"/>
       <c r="D49" s="27" t="s">
         <v>12</v>
       </c>
@@ -4155,9 +4155,9 @@
       <c r="K49" s="29"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="67"/>
-      <c r="B50" s="67"/>
-      <c r="C50" s="59"/>
+      <c r="A50" s="68"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="60"/>
       <c r="D50" s="27" t="s">
         <v>13</v>
       </c>
@@ -4180,9 +4180,9 @@
       <c r="K50" s="29"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="67"/>
-      <c r="B51" s="67"/>
-      <c r="C51" s="59"/>
+      <c r="A51" s="68"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="60"/>
       <c r="D51" s="27" t="s">
         <v>14</v>
       </c>
@@ -4205,34 +4205,34 @@
       <c r="K51" s="29"/>
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="67"/>
-      <c r="B52" s="69"/>
-      <c r="C52" s="60"/>
+      <c r="A52" s="68"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="61"/>
       <c r="D52" s="36" t="s">
         <v>15</v>
       </c>
       <c r="E52" s="31"/>
-      <c r="F52" s="86" t="s">
-        <v>247</v>
+      <c r="F52" s="55" t="s">
+        <v>244</v>
       </c>
       <c r="G52" s="37"/>
       <c r="H52" s="29" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J52" s="37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K52" s="37"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="61" t="s">
+      <c r="A53" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="B53" s="62"/>
-      <c r="C53" s="58" t="s">
+      <c r="B53" s="63"/>
+      <c r="C53" s="59" t="s">
         <v>103</v>
       </c>
       <c r="D53" s="25" t="s">
@@ -4252,14 +4252,14 @@
         <v>194</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K53" s="33"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="63"/>
-      <c r="B54" s="64"/>
-      <c r="C54" s="59"/>
+      <c r="A54" s="64"/>
+      <c r="B54" s="65"/>
+      <c r="C54" s="60"/>
       <c r="D54" s="27" t="s">
         <v>40</v>
       </c>
@@ -4275,14 +4275,14 @@
         <v>187</v>
       </c>
       <c r="J54" s="29" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K54" s="29"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="63"/>
-      <c r="B55" s="64"/>
-      <c r="C55" s="59"/>
+      <c r="A55" s="64"/>
+      <c r="B55" s="65"/>
+      <c r="C55" s="60"/>
       <c r="D55" s="27" t="s">
         <v>41</v>
       </c>
@@ -4298,14 +4298,14 @@
         <v>195</v>
       </c>
       <c r="J55" s="29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K55" s="29"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="63"/>
-      <c r="B56" s="64"/>
-      <c r="C56" s="59"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="65"/>
+      <c r="C56" s="60"/>
       <c r="D56" s="27" t="s">
         <v>49</v>
       </c>
@@ -4321,14 +4321,14 @@
         <v>196</v>
       </c>
       <c r="J56" s="29" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K56" s="29"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="63"/>
-      <c r="B57" s="64"/>
-      <c r="C57" s="59"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="65"/>
+      <c r="C57" s="60"/>
       <c r="D57" s="27" t="s">
         <v>50</v>
       </c>
@@ -4344,14 +4344,14 @@
         <v>197</v>
       </c>
       <c r="J57" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K57" s="29"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="65"/>
-      <c r="B58" s="66"/>
-      <c r="C58" s="60"/>
+      <c r="A58" s="66"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="61"/>
       <c r="D58" s="31" t="s">
         <v>51</v>
       </c>
@@ -4367,35 +4367,35 @@
         <v>198</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K58" s="37"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="55" t="str">
+      <c r="A59" s="56" t="str">
         <f>"Total: "&amp;TEXT(SUM(E59:K59),"0")</f>
-        <v>Total: 790</v>
-      </c>
-      <c r="B59" s="55"/>
-      <c r="C59" s="55"/>
-      <c r="D59" s="55"/>
+        <v>Total: 847</v>
+      </c>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
       <c r="E59" s="52">
         <v>49</v>
       </c>
       <c r="F59" s="54">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G59" s="53">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H59" s="53">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="I59" s="53">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="J59" s="53">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K59" s="53">
         <v>1</v>
@@ -4454,173 +4454,173 @@
       <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74">
+      <c r="A2" s="75">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="82" t="s">
         <v>199</v>
       </c>
       <c r="C2" s="47" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="65" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="82"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="83"/>
       <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="84"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="82"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="75"/>
-      <c r="B5" s="82"/>
+      <c r="A5" s="76"/>
+      <c r="B5" s="83"/>
       <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="75"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="76"/>
+      <c r="B6" s="83"/>
       <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="84"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="75"/>
-      <c r="B7" s="82"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="83"/>
       <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="75"/>
-      <c r="B8" s="82"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="83"/>
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="48"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="75"/>
-      <c r="B9" s="82"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="83"/>
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
-      <c r="B10" s="82"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="83"/>
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="16"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
-      <c r="B11" s="82"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="83"/>
       <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="16"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
-      <c r="B12" s="82"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="83"/>
       <c r="C12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="76"/>
-      <c r="B13" s="82"/>
+      <c r="A13" s="77"/>
+      <c r="B13" s="83"/>
       <c r="C13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="16"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="74">
+      <c r="A14" s="75">
         <v>2</v>
       </c>
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="83" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -4628,121 +4628,121 @@
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="64" t="s">
+      <c r="F14" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="65"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="75"/>
-      <c r="B15" s="82"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="75"/>
-      <c r="B16" s="82"/>
+      <c r="A16" s="76"/>
+      <c r="B16" s="83"/>
       <c r="C16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="75"/>
-      <c r="B17" s="82"/>
+      <c r="A17" s="76"/>
+      <c r="B17" s="83"/>
       <c r="C17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="77"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
-      <c r="B18" s="82"/>
+      <c r="A18" s="76"/>
+      <c r="B18" s="83"/>
       <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="72" t="s">
+      <c r="E18" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
-      <c r="B19" s="82"/>
+      <c r="A19" s="76"/>
+      <c r="B19" s="83"/>
       <c r="C19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
-      <c r="B20" s="82"/>
+      <c r="A20" s="76"/>
+      <c r="B20" s="83"/>
       <c r="C20" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="72" t="s">
+      <c r="E20" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="76"/>
-      <c r="B21" s="82"/>
+      <c r="A21" s="77"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="73"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="74">
+      <c r="A22" s="75">
         <v>3</v>
       </c>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="79" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -4752,17 +4752,17 @@
       <c r="E22" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="F22" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="64"/>
+      <c r="H22" s="65"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="75"/>
-      <c r="B23" s="79"/>
+      <c r="A23" s="76"/>
+      <c r="B23" s="80"/>
       <c r="C23" s="6" t="s">
         <v>12</v>
       </c>
@@ -4770,13 +4770,13 @@
       <c r="E23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="75"/>
-      <c r="B24" s="79"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="80"/>
       <c r="C24" s="6" t="s">
         <v>40</v>
       </c>
@@ -4784,13 +4784,13 @@
       <c r="E24" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="75"/>
-      <c r="B25" s="79"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="6" t="s">
         <v>41</v>
       </c>
@@ -4798,50 +4798,50 @@
       <c r="E25" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="75"/>
-      <c r="B26" s="79"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="80"/>
       <c r="C26" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="72" t="s">
+      <c r="E26" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="75"/>
-      <c r="B27" s="79"/>
+      <c r="A27" s="76"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
-      <c r="B28" s="79"/>
+      <c r="A28" s="76"/>
+      <c r="B28" s="80"/>
       <c r="C28" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="76"/>
+      <c r="A29" s="77"/>
       <c r="B29" s="1" t="s">
         <v>35</v>
       </c>
@@ -4858,13 +4858,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H2:H28"/>
-    <mergeCell ref="F14:F21"/>
-    <mergeCell ref="F2:F13"/>
-    <mergeCell ref="G14:G21"/>
-    <mergeCell ref="G2:G13"/>
-    <mergeCell ref="F22:F28"/>
-    <mergeCell ref="G22:G28"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="A14:A21"/>
@@ -4876,6 +4869,13 @@
     <mergeCell ref="B14:B21"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E2:E7"/>
+    <mergeCell ref="H2:H28"/>
+    <mergeCell ref="F14:F21"/>
+    <mergeCell ref="F2:F13"/>
+    <mergeCell ref="G14:G21"/>
+    <mergeCell ref="G2:G13"/>
+    <mergeCell ref="F22:F28"/>
+    <mergeCell ref="G22:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/feature engineering.xlsx
+++ b/feature engineering.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repository\thesis\bitcoin-trend-prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE7A0C8-58E2-44E7-890B-CBF5607EFC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7406A5F5-183D-4D62-90FF-67B6718070C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4417,6 +4417,7 @@
     <mergeCell ref="B2:B40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4858,6 +4859,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H2:H28"/>
+    <mergeCell ref="F14:F21"/>
+    <mergeCell ref="F2:F13"/>
+    <mergeCell ref="G14:G21"/>
+    <mergeCell ref="G2:G13"/>
+    <mergeCell ref="F22:F28"/>
+    <mergeCell ref="G22:G28"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="A14:A21"/>
@@ -4869,13 +4877,6 @@
     <mergeCell ref="B14:B21"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E2:E7"/>
-    <mergeCell ref="H2:H28"/>
-    <mergeCell ref="F14:F21"/>
-    <mergeCell ref="F2:F13"/>
-    <mergeCell ref="G14:G21"/>
-    <mergeCell ref="G2:G13"/>
-    <mergeCell ref="F22:F28"/>
-    <mergeCell ref="G22:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
